--- a/java/shiftsolver/testSmallSolved.xlsx
+++ b/java/shiftsolver/testSmallSolved.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\milan\code\ShiftSolver\java\shiftsolver\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69BFD894-A3B6-44CC-AC7B-0CC01C4176BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D667BCD3-4C28-4F9E-92DA-5C5328EC4FE4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-75" yWindow="-16320" windowWidth="29040" windowHeight="15990" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-75" yWindow="-16320" windowWidth="29040" windowHeight="15990" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Einstellungen" sheetId="5" r:id="rId1"/>
@@ -281,12 +281,6 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF242424"/>
-      <name val="Aptos Narrow"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -333,8 +327,15 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF242424"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
   </fonts>
-  <fills count="13">
+  <fills count="15">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -407,6 +408,17 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="none">
+        <fgColor indexed="16"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="16"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="46">
     <border>
@@ -1005,31 +1017,31 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="13" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyFill="true">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="13" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyFill="true">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="13" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyFill="true">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="14" borderId="5" xfId="0" applyFont="1" applyFill="true" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="13" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyFill="true">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="14" borderId="7" xfId="0" applyFont="1" applyFill="true" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="14" borderId="7" xfId="0" applyFont="1" applyFill="true" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="14" borderId="6" xfId="0" applyFont="1" applyFill="true" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="14" borderId="4" xfId="0" applyFont="1" applyFill="true" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1107,33 +1119,30 @@
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="13" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyFill="true">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="14" borderId="5" xfId="0" applyFont="1" applyFill="true" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="13" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyFill="true">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="14" borderId="7" xfId="0" applyFont="1" applyFill="true" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="13" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyFill="true">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="14" borderId="2" xfId="0" applyFont="1" applyFill="true" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1152,7 +1161,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="16" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1181,7 +1190,7 @@
         </ext>
       </extLst>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="9" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
       <extLst>
         <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
@@ -1189,7 +1198,7 @@
         </ext>
       </extLst>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="9" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="9" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
       <extLst>
         <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
@@ -1197,7 +1206,7 @@
         </ext>
       </extLst>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="9" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="9" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
       <extLst>
         <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
@@ -1239,7 +1248,7 @@
     <xf numFmtId="164" fontId="0" fillId="6" borderId="43" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="43" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="24" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="23" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="164" fontId="2" fillId="5" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
@@ -1278,20 +1287,23 @@
     <xf numFmtId="164" fontId="7" fillId="9" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="24" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
@@ -1667,28 +1679,28 @@
     <col min="1" max="1" customWidth="true" width="20.77734375"/>
     <col min="2" max="2" bestFit="true" customWidth="true" width="11.88671875"/>
     <col min="3" max="3" customWidth="true" width="70.88671875"/>
-    <col min="4" max="4" customWidth="true" style="96" width="18.0"/>
+    <col min="4" max="4" customWidth="true" style="95" width="18.0"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A1" s="85" t="s">
+      <c r="A1" s="84" t="s">
         <v>23</v>
       </c>
-      <c r="B1" s="84"/>
-      <c r="C1" s="84"/>
-      <c r="D1" s="101"/>
+      <c r="B1" s="83"/>
+      <c r="C1" s="83"/>
+      <c r="D1" s="100"/>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A2" s="41" t="s">
+      <c r="A2" s="105" t="s">
         <v>25</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C2" s="42" t="s">
+      <c r="C2" s="41" t="s">
         <v>0</v>
       </c>
-      <c r="D2" s="97"/>
+      <c r="D2" s="96"/>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
@@ -1697,7 +1709,7 @@
       <c r="B3" s="3">
         <v>3.5</v>
       </c>
-      <c r="C3" s="43" t="s">
+      <c r="C3" s="42" t="s">
         <v>2</v>
       </c>
     </row>
@@ -1708,7 +1720,7 @@
       <c r="B4" s="3">
         <v>7.5</v>
       </c>
-      <c r="C4" s="43" t="s">
+      <c r="C4" s="42" t="s">
         <v>4</v>
       </c>
     </row>
@@ -1719,7 +1731,7 @@
       <c r="B5" s="3">
         <v>7</v>
       </c>
-      <c r="C5" s="43" t="s">
+      <c r="C5" s="42" t="s">
         <v>6</v>
       </c>
     </row>
@@ -1730,7 +1742,7 @@
       <c r="B6" s="3">
         <v>10</v>
       </c>
-      <c r="C6" s="100" t="s">
+      <c r="C6" s="99" t="s">
         <v>8</v>
       </c>
     </row>
@@ -1741,17 +1753,17 @@
       <c r="B7" s="3">
         <v>4.5</v>
       </c>
-      <c r="C7" s="100" t="s">
+      <c r="C7" s="99" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A8" s="103" t="s">
+      <c r="A8" s="102" t="s">
         <v>32</v>
       </c>
-      <c r="B8" s="102"/>
-      <c r="C8" s="104"/>
-      <c r="D8" s="101"/>
+      <c r="B8" s="101"/>
+      <c r="C8" s="103"/>
+      <c r="D8" s="100"/>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" s="3" t="s">
@@ -1774,15 +1786,15 @@
       <c r="D10" s="3"/>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A11" s="85" t="s">
+      <c r="A11" s="84" t="s">
         <v>22</v>
       </c>
-      <c r="B11" s="85"/>
-      <c r="C11" s="85"/>
-      <c r="D11" s="101"/>
+      <c r="B11" s="84"/>
+      <c r="C11" s="84"/>
+      <c r="D11" s="100"/>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A12" s="105" t="s">
+      <c r="A12" s="104" t="s">
         <v>26</v>
       </c>
       <c r="B12" t="s" s="0">
@@ -1791,12 +1803,12 @@
       <c r="C12" t="s" s="0">
         <v>15</v>
       </c>
-      <c r="D12" s="96" t="s">
+      <c r="D12" s="95" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A13" s="105" t="s">
+      <c r="A13" s="104" t="s">
         <v>28</v>
       </c>
       <c r="B13" t="s" s="0">
@@ -1804,7 +1816,7 @@
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A14" s="105" t="s">
+      <c r="A14" s="104" t="s">
         <v>29</v>
       </c>
       <c r="B14" t="s" s="0">
@@ -1812,7 +1824,7 @@
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A15" s="105" t="s">
+      <c r="A15" s="104" t="s">
         <v>30</v>
       </c>
       <c r="B15" t="s" s="0">
@@ -1820,7 +1832,7 @@
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A16" s="105" t="s">
+      <c r="A16" s="104" t="s">
         <v>31</v>
       </c>
       <c r="B16" t="s" s="0">
@@ -1861,49 +1873,51 @@
       <c r="B1" s="31" t="s">
         <v>15</v>
       </c>
-      <c r="C1" s="58" t="s">
+      <c r="C1" s="57" t="s">
         <v>16</v>
       </c>
-      <c r="D1" s="59" t="s">
+      <c r="D1" s="58" t="s">
         <v>20</v>
       </c>
-      <c r="E1" s="60" t="s">
+      <c r="E1" s="59" t="s">
         <v>19</v>
       </c>
-      <c r="F1" s="60" t="s">
+      <c r="F1" s="59" t="s">
         <v>18</v>
       </c>
-      <c r="G1" s="60" t="s">
+      <c r="G1" s="59" t="s">
         <v>17</v>
       </c>
       <c r="H1" s="32"/>
     </row>
     <row r="2" spans="1:285" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="86">
+      <c r="A2" s="85">
         <v>45597</v>
       </c>
-      <c r="B2" s="56" t="s">
+      <c r="B2" s="55" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="46">
+      <c r="C2" s="45">
         <f t="shared" ref="C2:C35" si="0">COUNTIF(D2:G2,"&gt;1")</f>
         <v>2</v>
       </c>
-      <c r="D2" s="45"/>
-      <c r="E2" s="44"/>
-      <c r="F2" s="45">
+      <c r="D2" s="44">
         <v>7</v>
       </c>
-      <c r="G2" s="45"/>
+      <c r="E2" s="43"/>
+      <c r="F2" s="44">
+        <v>7</v>
+      </c>
+      <c r="G2" s="44"/>
       <c r="H2" s="34"/>
       <c r="I2" s="26"/>
     </row>
     <row r="3" spans="1:285" s="1" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="87"/>
-      <c r="B3" s="55" t="s">
+      <c r="A3" s="86"/>
+      <c r="B3" s="54" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="47">
+      <c r="C3" s="46">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
@@ -1911,7 +1925,9 @@
         <v>10</v>
       </c>
       <c r="E3" s="10"/>
-      <c r="F3" s="15"/>
+      <c r="F3" s="15">
+        <v>10</v>
+      </c>
       <c r="G3" s="15"/>
       <c r="H3" s="34"/>
       <c r="I3" s="26"/>
@@ -2193,38 +2209,46 @@
       <c r="JY3" s="0"/>
     </row>
     <row r="4" spans="1:285" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="91">
+      <c r="A4" s="90">
         <f>A2+1</f>
         <v>45598</v>
       </c>
       <c r="B4" s="18" t="s">
         <v>5</v>
       </c>
-      <c r="C4" s="47">
+      <c r="C4" s="46">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="D4" s="8"/>
+      <c r="D4" s="8">
+        <v>7</v>
+      </c>
       <c r="E4" s="11"/>
       <c r="F4" s="8">
         <v>7</v>
       </c>
-      <c r="G4" s="8"/>
+      <c r="G4" s="8">
+        <v>7</v>
+      </c>
       <c r="H4" s="32"/>
       <c r="I4" s="26"/>
     </row>
     <row r="5" spans="1:285" s="2" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="92"/>
+      <c r="A5" s="91"/>
       <c r="B5" s="17" t="s">
         <v>7</v>
       </c>
-      <c r="C5" s="47">
+      <c r="C5" s="46">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="D5" s="50"/>
-      <c r="E5" s="12"/>
-      <c r="F5" s="14"/>
+      <c r="D5" s="49"/>
+      <c r="E5" s="12">
+        <v>10</v>
+      </c>
+      <c r="F5" s="14">
+        <v>10</v>
+      </c>
       <c r="G5" s="14">
         <v>10</v>
       </c>
@@ -2508,37 +2532,43 @@
       <c r="JY5" s="0"/>
     </row>
     <row r="6" spans="1:285" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="91">
+      <c r="A6" s="90">
         <f>A4+1</f>
         <v>45599</v>
       </c>
       <c r="B6" s="18" t="s">
         <v>5</v>
       </c>
-      <c r="C6" s="47">
+      <c r="C6" s="46">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="D6" s="49">
+      <c r="D6" s="48">
         <v>7</v>
       </c>
       <c r="E6" s="11"/>
-      <c r="F6" s="8"/>
+      <c r="F6" s="8">
+        <v>7</v>
+      </c>
       <c r="G6" s="8"/>
       <c r="H6" s="35"/>
       <c r="I6" s="26"/>
     </row>
     <row r="7" spans="1:285" s="1" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="92"/>
+      <c r="A7" s="91"/>
       <c r="B7" s="17" t="s">
         <v>3</v>
       </c>
-      <c r="C7" s="47">
+      <c r="C7" s="46">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="D7" s="50"/>
-      <c r="E7" s="12"/>
+      <c r="D7" s="49">
+        <v>7.5</v>
+      </c>
+      <c r="E7" s="12">
+        <v>7.5</v>
+      </c>
       <c r="F7" s="12">
         <v>7.5</v>
       </c>
@@ -2823,41 +2853,49 @@
       <c r="JY7" s="0"/>
     </row>
     <row r="8" spans="1:285" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="89">
+      <c r="A8" s="88">
         <f>A6+1</f>
         <v>45600</v>
       </c>
       <c r="B8" s="18" t="s">
         <v>1</v>
       </c>
-      <c r="C8" s="47">
+      <c r="C8" s="46">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="D8" s="51"/>
+      <c r="D8" s="50"/>
       <c r="E8" s="9">
         <v>3.5</v>
       </c>
-      <c r="F8" s="9"/>
-      <c r="G8" s="9"/>
+      <c r="F8" s="9">
+        <v>3.5</v>
+      </c>
+      <c r="G8" s="9">
+        <v>3.5</v>
+      </c>
       <c r="H8" s="32"/>
       <c r="I8" s="26"/>
     </row>
     <row r="9" spans="1:285" s="1" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="90"/>
+      <c r="A9" s="89"/>
       <c r="B9" s="17" t="s">
         <v>3</v>
       </c>
-      <c r="C9" s="47">
+      <c r="C9" s="46">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="D9" s="50"/>
-      <c r="E9" s="13"/>
+      <c r="D9" s="49"/>
+      <c r="E9" s="13">
+        <v>7.5</v>
+      </c>
       <c r="F9" s="13">
         <v>7.5</v>
       </c>
-      <c r="G9" s="13"/>
+      <c r="G9" s="13">
+        <v>7.5</v>
+      </c>
       <c r="H9" s="32"/>
       <c r="I9" s="26"/>
       <c r="J9" s="0"/>
@@ -3138,37 +3176,41 @@
       <c r="JY9" s="0"/>
     </row>
     <row r="10" spans="1:285" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="88">
+      <c r="A10" s="87">
         <f>A8+1</f>
         <v>45601</v>
       </c>
       <c r="B10" s="18" t="s">
         <v>1</v>
       </c>
-      <c r="C10" s="47">
+      <c r="C10" s="46">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="D10" s="49"/>
+      <c r="D10" s="48"/>
       <c r="E10" s="11">
         <v>3.5</v>
       </c>
-      <c r="F10" s="11"/>
+      <c r="F10" s="11">
+        <v>3.5</v>
+      </c>
       <c r="G10" s="11"/>
       <c r="H10" s="36"/>
       <c r="I10" s="26"/>
     </row>
     <row r="11" spans="1:285" s="1" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="88"/>
+      <c r="A11" s="87"/>
       <c r="B11" s="17" t="s">
         <v>3</v>
       </c>
-      <c r="C11" s="47">
+      <c r="C11" s="46">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="D11" s="50"/>
-      <c r="E11" s="13"/>
+      <c r="D11" s="49"/>
+      <c r="E11" s="13">
+        <v>7.5</v>
+      </c>
       <c r="F11" s="13">
         <v>7.5</v>
       </c>
@@ -3453,14 +3495,14 @@
       <c r="JY11" s="0"/>
     </row>
     <row r="12" spans="1:285" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="88">
+      <c r="A12" s="87">
         <f>A10+1</f>
         <v>45602</v>
       </c>
       <c r="B12" s="19" t="s">
         <v>1</v>
       </c>
-      <c r="C12" s="47">
+      <c r="C12" s="46">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
@@ -3474,15 +3516,15 @@
       <c r="I12" s="26"/>
     </row>
     <row r="13" spans="1:285" s="1" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="88"/>
+      <c r="A13" s="87"/>
       <c r="B13" s="17" t="s">
         <v>3</v>
       </c>
-      <c r="C13" s="47">
+      <c r="C13" s="46">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="D13" s="50"/>
+      <c r="D13" s="49"/>
       <c r="E13" s="13"/>
       <c r="F13" s="16"/>
       <c r="G13" s="13">
@@ -3768,37 +3810,41 @@
       <c r="JY13" s="0"/>
     </row>
     <row r="14" spans="1:285" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="88">
+      <c r="A14" s="87">
         <f>A12+1</f>
         <v>45603</v>
       </c>
       <c r="B14" s="18" t="s">
         <v>1</v>
       </c>
-      <c r="C14" s="47">
+      <c r="C14" s="46">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="D14" s="49"/>
+      <c r="D14" s="48"/>
       <c r="E14" s="11">
         <v>3.5</v>
       </c>
       <c r="F14" s="8"/>
-      <c r="G14" s="11"/>
+      <c r="G14" s="11">
+        <v>3.5</v>
+      </c>
       <c r="H14" s="32"/>
       <c r="I14" s="26"/>
     </row>
     <row r="15" spans="1:285" s="1" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="88"/>
+      <c r="A15" s="87"/>
       <c r="B15" s="20" t="s">
         <v>3</v>
       </c>
-      <c r="C15" s="47">
+      <c r="C15" s="46">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="D15" s="52"/>
-      <c r="E15" s="13"/>
+      <c r="D15" s="51"/>
+      <c r="E15" s="13">
+        <v>7.5</v>
+      </c>
       <c r="F15" s="16"/>
       <c r="G15" s="13">
         <v>7.5</v>
@@ -4083,57 +4129,65 @@
       <c r="JY15" s="0"/>
     </row>
     <row r="16" spans="1:285" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="88">
+      <c r="A16" s="87">
         <f>A14+1</f>
         <v>45604</v>
       </c>
       <c r="B16" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="C16" s="47">
+      <c r="C16" s="46">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="D16" s="49">
+      <c r="D16" s="48">
         <v>4.5</v>
       </c>
       <c r="E16" s="11"/>
-      <c r="F16" s="8"/>
+      <c r="F16" s="8">
+        <v>4.5</v>
+      </c>
       <c r="G16" s="8"/>
       <c r="H16" s="37"/>
       <c r="I16" s="27"/>
     </row>
     <row r="17" spans="1:291" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="88"/>
+      <c r="A17" s="87"/>
       <c r="B17" s="20" t="s">
         <v>7</v>
       </c>
-      <c r="C17" s="47">
+      <c r="C17" s="46">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="D17" s="48">
+      <c r="D17" s="47">
         <v>10</v>
       </c>
-      <c r="E17" s="10"/>
-      <c r="F17" s="15"/>
+      <c r="E17" s="10">
+        <v>10</v>
+      </c>
+      <c r="F17" s="15">
+        <v>10</v>
+      </c>
       <c r="G17" s="15"/>
       <c r="H17" s="38"/>
       <c r="I17" s="28"/>
     </row>
     <row r="18" spans="1:291" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="93">
+      <c r="A18" s="92">
         <f>A16+1</f>
         <v>45605</v>
       </c>
       <c r="B18" s="18" t="s">
         <v>5</v>
       </c>
-      <c r="C18" s="47">
+      <c r="C18" s="46">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="D18" s="51"/>
+      <c r="D18" s="50">
+        <v>7</v>
+      </c>
       <c r="E18" s="9"/>
       <c r="F18" s="7">
         <v>7</v>
@@ -4143,94 +4197,110 @@
       <c r="I18" s="26"/>
     </row>
     <row r="19" spans="1:291" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="93"/>
+      <c r="A19" s="92"/>
       <c r="B19" s="21" t="s">
         <v>7</v>
       </c>
-      <c r="C19" s="47">
+      <c r="C19" s="46">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="D19" s="53">
+      <c r="D19" s="52">
         <v>10</v>
       </c>
       <c r="E19" s="22"/>
       <c r="F19" s="23"/>
-      <c r="G19" s="53"/>
+      <c r="G19" s="52">
+        <v>10</v>
+      </c>
       <c r="H19" s="32"/>
       <c r="I19" s="26"/>
     </row>
     <row r="20" spans="1:291" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="93">
+      <c r="A20" s="92">
         <f>A18+1</f>
         <v>45606</v>
       </c>
       <c r="B20" s="18" t="s">
         <v>5</v>
       </c>
-      <c r="C20" s="47">
+      <c r="C20" s="46">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="D20" s="49"/>
+      <c r="D20" s="48">
+        <v>7</v>
+      </c>
       <c r="E20" s="11"/>
       <c r="F20" s="8"/>
-      <c r="G20" s="49">
+      <c r="G20" s="48">
         <v>7</v>
       </c>
       <c r="H20" s="32"/>
       <c r="I20" s="26"/>
     </row>
     <row r="21" spans="1:291" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="93"/>
+      <c r="A21" s="92"/>
       <c r="B21" s="20" t="s">
         <v>3</v>
       </c>
-      <c r="C21" s="47">
+      <c r="C21" s="46">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="D21" s="12"/>
+      <c r="D21" s="12">
+        <v>7.5</v>
+      </c>
       <c r="E21" s="12">
         <v>7.5</v>
       </c>
       <c r="F21" s="14"/>
-      <c r="G21" s="12"/>
+      <c r="G21" s="12">
+        <v>7.5</v>
+      </c>
       <c r="H21" s="32"/>
       <c r="I21" s="26"/>
     </row>
     <row r="22" spans="1:291" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="88">
+      <c r="A22" s="87">
         <f>A20+1</f>
         <v>45607</v>
       </c>
       <c r="B22" s="18" t="s">
         <v>1</v>
       </c>
-      <c r="C22" s="47">
+      <c r="C22" s="46">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
       <c r="D22" s="11">
         <v>3.5</v>
       </c>
-      <c r="E22" s="11"/>
+      <c r="E22" s="11">
+        <v>3.5</v>
+      </c>
       <c r="F22" s="8"/>
-      <c r="G22" s="11"/>
+      <c r="G22" s="11">
+        <v>3.5</v>
+      </c>
       <c r="H22" s="32"/>
       <c r="I22" s="26"/>
     </row>
     <row r="23" spans="1:291" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="88"/>
+      <c r="A23" s="87"/>
       <c r="B23" s="20" t="s">
         <v>3</v>
       </c>
-      <c r="C23" s="47">
+      <c r="C23" s="46">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="D23" s="12"/>
-      <c r="E23" s="12"/>
+      <c r="D23" s="12">
+        <v>7.5</v>
+      </c>
+      <c r="E23" s="12">
+        <v>7.5</v>
+      </c>
       <c r="F23" s="14"/>
       <c r="G23" s="12">
         <v>7.5</v>
@@ -4239,37 +4309,45 @@
       <c r="I23" s="26"/>
     </row>
     <row r="24" spans="1:291" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="88">
+      <c r="A24" s="87">
         <f>A22+1</f>
         <v>45608</v>
       </c>
       <c r="B24" s="18" t="s">
         <v>1</v>
       </c>
-      <c r="C24" s="47">
+      <c r="C24" s="46">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="D24" s="9"/>
+      <c r="D24" s="9">
+        <v>3.5</v>
+      </c>
       <c r="E24" s="9">
         <v>3.5</v>
       </c>
-      <c r="F24" s="7"/>
+      <c r="F24" s="7">
+        <v>3.5</v>
+      </c>
       <c r="G24" s="7"/>
       <c r="H24" s="32"/>
       <c r="I24" s="26"/>
     </row>
     <row r="25" spans="1:291" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="88"/>
+      <c r="A25" s="87"/>
       <c r="B25" s="25" t="s">
         <v>3</v>
       </c>
-      <c r="C25" s="47">
+      <c r="C25" s="46">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="D25" s="10"/>
-      <c r="E25" s="10"/>
+      <c r="D25" s="10">
+        <v>7.5</v>
+      </c>
+      <c r="E25" s="10">
+        <v>7.5</v>
+      </c>
       <c r="F25" s="15">
         <v>7.5</v>
       </c>
@@ -4278,19 +4356,23 @@
       <c r="I25" s="26"/>
     </row>
     <row r="26" spans="1:291" s="4" customFormat="1" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A26" s="88">
+      <c r="A26" s="87">
         <f>A24+1</f>
         <v>45609</v>
       </c>
       <c r="B26" s="24" t="s">
         <v>1</v>
       </c>
-      <c r="C26" s="47">
+      <c r="C26" s="46">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="D26" s="11"/>
-      <c r="E26" s="11"/>
+      <c r="D26" s="11">
+        <v>3.5</v>
+      </c>
+      <c r="E26" s="11">
+        <v>3.5</v>
+      </c>
       <c r="F26" s="8"/>
       <c r="G26" s="11">
         <v>3.5</v>
@@ -4581,53 +4663,65 @@
       <c r="KE26" s="29"/>
     </row>
     <row r="27" spans="1:291" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="88"/>
+      <c r="A27" s="87"/>
       <c r="B27" s="17" t="s">
         <v>3</v>
       </c>
-      <c r="C27" s="47">
+      <c r="C27" s="46">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
       <c r="D27" s="13">
         <v>7.5</v>
       </c>
-      <c r="E27" s="13"/>
+      <c r="E27" s="13">
+        <v>7.5</v>
+      </c>
       <c r="F27" s="16"/>
-      <c r="G27" s="13"/>
+      <c r="G27" s="13">
+        <v>7.5</v>
+      </c>
       <c r="H27" s="40"/>
     </row>
     <row r="28" spans="1:291" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="89">
+      <c r="A28" s="88">
         <f>A26+1</f>
         <v>45610</v>
       </c>
       <c r="B28" s="18" t="s">
         <v>1</v>
       </c>
-      <c r="C28" s="47">
+      <c r="C28" s="46">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
       <c r="D28" s="11">
         <v>3.5</v>
       </c>
-      <c r="E28" s="11"/>
+      <c r="E28" s="11">
+        <v>3.5</v>
+      </c>
       <c r="F28" s="8"/>
-      <c r="G28" s="11"/>
+      <c r="G28" s="11">
+        <v>3.5</v>
+      </c>
       <c r="H28" s="33"/>
     </row>
     <row r="29" spans="1:291" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="90"/>
+      <c r="A29" s="89"/>
       <c r="B29" s="20" t="s">
         <v>3</v>
       </c>
-      <c r="C29" s="47">
+      <c r="C29" s="46">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="D29" s="13"/>
-      <c r="E29" s="13"/>
+      <c r="D29" s="13">
+        <v>7.5</v>
+      </c>
+      <c r="E29" s="13">
+        <v>7.5</v>
+      </c>
       <c r="F29" s="16"/>
       <c r="G29" s="13">
         <v>7.5</v>
@@ -4635,110 +4729,132 @@
       <c r="H29" s="33"/>
     </row>
     <row r="30" spans="1:291" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="94">
+      <c r="A30" s="93">
         <f>A28+1</f>
         <v>45611</v>
       </c>
       <c r="B30" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="C30" s="47">
+      <c r="C30" s="46">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="D30" s="48"/>
-      <c r="E30" s="49">
+      <c r="D30" s="47">
+        <v>10</v>
+      </c>
+      <c r="E30" s="48">
         <v>4.5</v>
       </c>
       <c r="F30" s="8"/>
-      <c r="G30" s="49"/>
+      <c r="G30" s="48">
+        <v>4.5</v>
+      </c>
       <c r="H30" s="33"/>
     </row>
     <row r="31" spans="1:291" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="95"/>
+      <c r="A31" s="94"/>
       <c r="B31" s="20" t="s">
         <v>7</v>
       </c>
-      <c r="C31" s="47">
+      <c r="C31" s="46">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="D31" s="51"/>
-      <c r="E31" s="48"/>
+      <c r="D31" s="50">
+        <v>7</v>
+      </c>
+      <c r="E31" s="47">
+        <v>10</v>
+      </c>
       <c r="F31" s="15"/>
-      <c r="G31" s="48">
+      <c r="G31" s="47">
         <v>10</v>
       </c>
       <c r="H31" s="33"/>
     </row>
     <row r="32" spans="1:291" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="93">
+      <c r="A32" s="92">
         <f>A30+1</f>
         <v>45612</v>
       </c>
       <c r="B32" s="18" t="s">
         <v>5</v>
       </c>
-      <c r="C32" s="47">
+      <c r="C32" s="46">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="D32" s="53">
+      <c r="D32" s="52">
         <v>10</v>
       </c>
-      <c r="E32" s="51"/>
+      <c r="E32" s="50">
+        <v>7</v>
+      </c>
       <c r="F32" s="7"/>
-      <c r="G32" s="51"/>
+      <c r="G32" s="50">
+        <v>7</v>
+      </c>
       <c r="H32" s="33"/>
     </row>
     <row r="33" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="93"/>
+      <c r="A33" s="92"/>
       <c r="B33" s="17" t="s">
         <v>7</v>
       </c>
-      <c r="C33" s="47">
+      <c r="C33" s="46">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="D33" s="54"/>
-      <c r="E33" s="53"/>
-      <c r="F33" s="6"/>
-      <c r="G33" s="53">
+      <c r="D33" s="53"/>
+      <c r="E33" s="52">
         <v>10</v>
       </c>
+      <c r="F33" s="6">
+        <v>10</v>
+      </c>
+      <c r="G33" s="52">
+        <v>10</v>
+      </c>
       <c r="H33" s="33"/>
     </row>
     <row r="34" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="93">
+      <c r="A34" s="92">
         <f>A32+1</f>
         <v>45613</v>
       </c>
       <c r="B34" s="18" t="s">
         <v>5</v>
       </c>
-      <c r="C34" s="47">
+      <c r="C34" s="46">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="D34" s="51"/>
-      <c r="E34" s="49">
+      <c r="D34" s="50"/>
+      <c r="E34" s="48">
         <v>7</v>
       </c>
-      <c r="F34" s="7"/>
-      <c r="G34" s="49"/>
+      <c r="F34" s="7">
+        <v>7</v>
+      </c>
+      <c r="G34" s="48">
+        <v>7</v>
+      </c>
       <c r="H34" s="33"/>
     </row>
     <row r="35" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="86"/>
-      <c r="B35" s="80" t="s">
+      <c r="A35" s="85"/>
+      <c r="B35" s="79" t="s">
         <v>3</v>
       </c>
-      <c r="C35" s="81">
+      <c r="C35" s="80">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="D35" s="50"/>
-      <c r="E35" s="12"/>
+      <c r="D35" s="49"/>
+      <c r="E35" s="12">
+        <v>7.5</v>
+      </c>
       <c r="F35" s="16"/>
       <c r="G35" s="12">
         <v>7.5</v>
@@ -4746,103 +4862,103 @@
       <c r="H35" s="33"/>
     </row>
     <row r="36" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A36" s="82"/>
-      <c r="B36" s="83"/>
-      <c r="C36" s="83"/>
-      <c r="D36" s="83"/>
-      <c r="E36" s="83"/>
-      <c r="F36" s="83"/>
-      <c r="G36" s="83"/>
+      <c r="A36" s="81"/>
+      <c r="B36" s="82"/>
+      <c r="C36" s="82"/>
+      <c r="D36" s="82"/>
+      <c r="E36" s="82"/>
+      <c r="F36" s="82"/>
+      <c r="G36" s="82"/>
       <c r="H36" s="33"/>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A37" s="98" t="s">
+      <c r="A37" s="97" t="s">
         <v>27</v>
       </c>
-      <c r="B37" s="99"/>
-      <c r="C37" s="65" t="s">
+      <c r="B37" s="98"/>
+      <c r="C37" s="64" t="s">
         <v>11</v>
       </c>
-      <c r="D37" s="72">
+      <c r="D37" s="71">
         <v>10</v>
       </c>
-      <c r="E37" s="73">
+      <c r="E37" s="72">
         <v>30</v>
       </c>
-      <c r="F37" s="73">
+      <c r="F37" s="72">
         <v>40</v>
       </c>
-      <c r="G37" s="74">
+      <c r="G37" s="73">
         <v>50</v>
       </c>
       <c r="H37" s="32"/>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A38" s="98"/>
-      <c r="B38" s="99"/>
-      <c r="C38" s="66" t="s">
+      <c r="A38" s="97"/>
+      <c r="B38" s="98"/>
+      <c r="C38" s="65" t="s">
         <v>12</v>
       </c>
-      <c r="D38" s="75">
+      <c r="D38" s="74">
         <v>100</v>
       </c>
-      <c r="E38" s="71">
+      <c r="E38" s="70">
         <v>100</v>
       </c>
-      <c r="F38" s="71">
+      <c r="F38" s="70">
         <v>80</v>
       </c>
-      <c r="G38" s="76">
+      <c r="G38" s="75">
         <v>120</v>
       </c>
       <c r="H38" s="32"/>
     </row>
     <row r="39" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A39" s="98"/>
-      <c r="B39" s="99"/>
-      <c r="C39" s="63" t="s">
+      <c r="A39" s="97"/>
+      <c r="B39" s="98"/>
+      <c r="C39" s="62" t="s">
         <v>13</v>
       </c>
-      <c r="D39" s="77">
+      <c r="D39" s="76">
         <f>SUM(D2:D35)</f>
         <v>155.5</v>
       </c>
-      <c r="E39" s="78">
+      <c r="E39" s="77">
         <f>SUM(E2:E35)</f>
         <v>158</v>
       </c>
-      <c r="F39" s="78">
+      <c r="F39" s="77">
         <f>SUM(F2:F35)</f>
         <v>120</v>
       </c>
-      <c r="G39" s="79">
+      <c r="G39" s="78">
         <f>SUM(G2:G35)</f>
         <v>153.5</v>
       </c>
       <c r="H39" s="32"/>
     </row>
     <row r="40" spans="1:8" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A40" s="61"/>
-      <c r="B40" s="62"/>
-      <c r="C40" s="64" t="s">
+      <c r="A40" s="60"/>
+      <c r="B40" s="61"/>
+      <c r="C40" s="63" t="s">
         <v>21</v>
       </c>
-      <c r="D40" s="67" t="b">
+      <c r="D40" s="66" t="b">
         <v>1</v>
       </c>
-      <c r="E40" s="68" t="b">
-        <v>0</v>
-      </c>
-      <c r="F40" s="69" t="b">
+      <c r="E40" s="67" t="b">
         <v>1</v>
       </c>
-      <c r="G40" s="70" t="b">
-        <v>0</v>
+      <c r="F40" s="68" t="b">
+        <v>1</v>
+      </c>
+      <c r="G40" s="69" t="b">
+        <v>1</v>
       </c>
       <c r="H40" s="32"/>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A41" s="57"/>
+      <c r="A41" s="56"/>
       <c r="B41" s="33"/>
       <c r="C41" s="33"/>
       <c r="D41" s="33"/>

--- a/java/shiftsolver/testSmallSolved.xlsx
+++ b/java/shiftsolver/testSmallSolved.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\milan\code\ShiftSolver\java\shiftsolver\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D667BCD3-4C28-4F9E-92DA-5C5328EC4FE4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9513D5BE-0A06-4C62-B72E-0E9D672C61E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-75" yWindow="-16320" windowWidth="29040" windowHeight="15990" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Einstellungen" sheetId="5" r:id="rId1"/>
@@ -335,7 +335,7 @@
       <charset val="1"/>
     </font>
   </fonts>
-  <fills count="15">
+  <fills count="13">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -408,17 +408,6 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="none">
-        <fgColor indexed="16"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor indexed="16"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="46">
     <border>
@@ -1005,7 +994,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="106">
+  <cellXfs count="105">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
@@ -1017,31 +1006,31 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="13" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyFill="true">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="13" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyFill="true">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="13" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyFill="true">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="14" borderId="5" xfId="0" applyFont="1" applyFill="true" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="13" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyFill="true">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="14" borderId="7" xfId="0" applyFont="1" applyFill="true" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="14" borderId="7" xfId="0" applyFont="1" applyFill="true" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="14" borderId="6" xfId="0" applyFont="1" applyFill="true" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="14" borderId="4" xfId="0" applyFont="1" applyFill="true" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1122,27 +1111,27 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="13" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyFill="true">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="14" borderId="5" xfId="0" applyFont="1" applyFill="true" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="13" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyFill="true">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="14" borderId="7" xfId="0" applyFont="1" applyFill="true" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="13" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyFill="true">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="14" borderId="2" xfId="0" applyFont="1" applyFill="true" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1249,44 +1238,7 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="43" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="23" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="164" fontId="2" fillId="5" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="5" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="5" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="5" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="5" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="164" fontId="7" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="9" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1303,6 +1255,42 @@
     <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="9" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="5" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="5" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="5" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="5" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="5" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1679,7 +1667,7 @@
     <col min="1" max="1" customWidth="true" width="20.77734375"/>
     <col min="2" max="2" bestFit="true" customWidth="true" width="11.88671875"/>
     <col min="3" max="3" customWidth="true" width="70.88671875"/>
-    <col min="4" max="4" customWidth="true" style="95" width="18.0"/>
+    <col min="4" max="4" customWidth="true" width="18.0"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
@@ -1688,10 +1676,10 @@
       </c>
       <c r="B1" s="83"/>
       <c r="C1" s="83"/>
-      <c r="D1" s="100"/>
+      <c r="D1" s="87"/>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A2" s="105" t="s">
+      <c r="A2" s="92" t="s">
         <v>25</v>
       </c>
       <c r="B2" s="3" t="s">
@@ -1700,7 +1688,7 @@
       <c r="C2" s="41" t="s">
         <v>0</v>
       </c>
-      <c r="D2" s="96"/>
+      <c r="D2" s="85"/>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
@@ -1742,7 +1730,7 @@
       <c r="B6" s="3">
         <v>10</v>
       </c>
-      <c r="C6" s="99" t="s">
+      <c r="C6" s="86" t="s">
         <v>8</v>
       </c>
     </row>
@@ -1753,17 +1741,17 @@
       <c r="B7" s="3">
         <v>4.5</v>
       </c>
-      <c r="C7" s="99" t="s">
+      <c r="C7" s="86" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A8" s="102" t="s">
+      <c r="A8" s="89" t="s">
         <v>32</v>
       </c>
-      <c r="B8" s="101"/>
-      <c r="C8" s="103"/>
-      <c r="D8" s="100"/>
+      <c r="B8" s="88"/>
+      <c r="C8" s="90"/>
+      <c r="D8" s="87"/>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" s="3" t="s">
@@ -1791,10 +1779,10 @@
       </c>
       <c r="B11" s="84"/>
       <c r="C11" s="84"/>
-      <c r="D11" s="100"/>
+      <c r="D11" s="87"/>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A12" s="104" t="s">
+      <c r="A12" s="91" t="s">
         <v>26</v>
       </c>
       <c r="B12" t="s" s="0">
@@ -1803,12 +1791,12 @@
       <c r="C12" t="s" s="0">
         <v>15</v>
       </c>
-      <c r="D12" s="95" t="s">
+      <c r="D12" t="s" s="0">
         <v>16</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A13" s="104" t="s">
+      <c r="A13" s="91" t="s">
         <v>28</v>
       </c>
       <c r="B13" t="s" s="0">
@@ -1816,7 +1804,7 @@
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A14" s="104" t="s">
+      <c r="A14" s="91" t="s">
         <v>29</v>
       </c>
       <c r="B14" t="s" s="0">
@@ -1824,7 +1812,7 @@
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A15" s="104" t="s">
+      <c r="A15" s="91" t="s">
         <v>30</v>
       </c>
       <c r="B15" t="s" s="0">
@@ -1832,7 +1820,7 @@
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A16" s="104" t="s">
+      <c r="A16" s="91" t="s">
         <v>31</v>
       </c>
       <c r="B16" t="s" s="0">
@@ -1891,7 +1879,7 @@
       <c r="H1" s="32"/>
     </row>
     <row r="2" spans="1:285" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="85">
+      <c r="A2" s="97">
         <v>45597</v>
       </c>
       <c r="B2" s="55" t="s">
@@ -1899,35 +1887,31 @@
       </c>
       <c r="C2" s="45">
         <f t="shared" ref="C2:C35" si="0">COUNTIF(D2:G2,"&gt;1")</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D2" s="44">
         <v>7</v>
       </c>
       <c r="E2" s="43"/>
-      <c r="F2" s="44">
-        <v>7</v>
-      </c>
+      <c r="F2" s="44"/>
       <c r="G2" s="44"/>
       <c r="H2" s="34"/>
       <c r="I2" s="26"/>
     </row>
     <row r="3" spans="1:285" s="1" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="86"/>
+      <c r="A3" s="102"/>
       <c r="B3" s="54" t="s">
         <v>7</v>
       </c>
       <c r="C3" s="46">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D3" s="15">
         <v>10</v>
       </c>
       <c r="E3" s="10"/>
-      <c r="F3" s="15">
-        <v>10</v>
-      </c>
+      <c r="F3" s="15"/>
       <c r="G3" s="15"/>
       <c r="H3" s="34"/>
       <c r="I3" s="26"/>
@@ -2209,7 +2193,7 @@
       <c r="JY3" s="0"/>
     </row>
     <row r="4" spans="1:285" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="90">
+      <c r="A4" s="103">
         <f>A2+1</f>
         <v>45598</v>
       </c>
@@ -2220,38 +2204,30 @@
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="D4" s="8">
-        <v>7</v>
-      </c>
+      <c r="D4" s="8"/>
       <c r="E4" s="11"/>
       <c r="F4" s="8">
         <v>7</v>
       </c>
-      <c r="G4" s="8">
-        <v>7</v>
-      </c>
+      <c r="G4" s="8"/>
       <c r="H4" s="32"/>
       <c r="I4" s="26"/>
     </row>
     <row r="5" spans="1:285" s="2" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="91"/>
+      <c r="A5" s="104"/>
       <c r="B5" s="17" t="s">
         <v>7</v>
       </c>
       <c r="C5" s="46">
         <f t="shared" si="0"/>
-        <v>3</v>
-      </c>
-      <c r="D5" s="49"/>
-      <c r="E5" s="12">
+        <v>1</v>
+      </c>
+      <c r="D5" s="49">
         <v>10</v>
       </c>
-      <c r="F5" s="14">
-        <v>10</v>
-      </c>
-      <c r="G5" s="14">
-        <v>10</v>
-      </c>
+      <c r="E5" s="12"/>
+      <c r="F5" s="14"/>
+      <c r="G5" s="14"/>
       <c r="H5" s="32"/>
       <c r="I5" s="26"/>
       <c r="J5" s="0"/>
@@ -2532,7 +2508,7 @@
       <c r="JY5" s="0"/>
     </row>
     <row r="6" spans="1:285" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="90">
+      <c r="A6" s="103">
         <f>A4+1</f>
         <v>45599</v>
       </c>
@@ -2547,15 +2523,13 @@
         <v>7</v>
       </c>
       <c r="E6" s="11"/>
-      <c r="F6" s="8">
-        <v>7</v>
-      </c>
+      <c r="F6" s="8"/>
       <c r="G6" s="8"/>
       <c r="H6" s="35"/>
       <c r="I6" s="26"/>
     </row>
     <row r="7" spans="1:285" s="1" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="91"/>
+      <c r="A7" s="104"/>
       <c r="B7" s="17" t="s">
         <v>3</v>
       </c>
@@ -2563,15 +2537,11 @@
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="D7" s="49">
-        <v>7.5</v>
-      </c>
+      <c r="D7" s="49"/>
       <c r="E7" s="12">
         <v>7.5</v>
       </c>
-      <c r="F7" s="12">
-        <v>7.5</v>
-      </c>
+      <c r="F7" s="12"/>
       <c r="G7" s="16"/>
       <c r="H7" s="32"/>
       <c r="I7" s="26"/>
@@ -2853,7 +2823,7 @@
       <c r="JY7" s="0"/>
     </row>
     <row r="8" spans="1:285" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="88">
+      <c r="A8" s="98">
         <f>A6+1</f>
         <v>45600</v>
       </c>
@@ -2862,40 +2832,32 @@
       </c>
       <c r="C8" s="46">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D8" s="50"/>
-      <c r="E8" s="9">
-        <v>3.5</v>
-      </c>
+      <c r="E8" s="9"/>
       <c r="F8" s="9">
         <v>3.5</v>
       </c>
-      <c r="G8" s="9">
-        <v>3.5</v>
-      </c>
+      <c r="G8" s="9"/>
       <c r="H8" s="32"/>
       <c r="I8" s="26"/>
     </row>
     <row r="9" spans="1:285" s="1" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="89"/>
+      <c r="A9" s="99"/>
       <c r="B9" s="17" t="s">
         <v>3</v>
       </c>
       <c r="C9" s="46">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D9" s="49"/>
       <c r="E9" s="13">
         <v>7.5</v>
       </c>
-      <c r="F9" s="13">
-        <v>7.5</v>
-      </c>
-      <c r="G9" s="13">
-        <v>7.5</v>
-      </c>
+      <c r="F9" s="13"/>
+      <c r="G9" s="13"/>
       <c r="H9" s="32"/>
       <c r="I9" s="26"/>
       <c r="J9" s="0"/>
@@ -3176,7 +3138,7 @@
       <c r="JY9" s="0"/>
     </row>
     <row r="10" spans="1:285" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="87">
+      <c r="A10" s="93">
         <f>A8+1</f>
         <v>45601</v>
       </c>
@@ -3185,32 +3147,28 @@
       </c>
       <c r="C10" s="46">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D10" s="48"/>
       <c r="E10" s="11">
         <v>3.5</v>
       </c>
-      <c r="F10" s="11">
-        <v>3.5</v>
-      </c>
+      <c r="F10" s="11"/>
       <c r="G10" s="11"/>
       <c r="H10" s="36"/>
       <c r="I10" s="26"/>
     </row>
     <row r="11" spans="1:285" s="1" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="87"/>
+      <c r="A11" s="93"/>
       <c r="B11" s="17" t="s">
         <v>3</v>
       </c>
       <c r="C11" s="46">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D11" s="49"/>
-      <c r="E11" s="13">
-        <v>7.5</v>
-      </c>
+      <c r="E11" s="13"/>
       <c r="F11" s="13">
         <v>7.5</v>
       </c>
@@ -3495,7 +3453,7 @@
       <c r="JY11" s="0"/>
     </row>
     <row r="12" spans="1:285" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="87">
+      <c r="A12" s="93">
         <f>A10+1</f>
         <v>45602</v>
       </c>
@@ -3516,7 +3474,7 @@
       <c r="I12" s="26"/>
     </row>
     <row r="13" spans="1:285" s="1" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="87"/>
+      <c r="A13" s="93"/>
       <c r="B13" s="17" t="s">
         <v>3</v>
       </c>
@@ -3810,7 +3768,7 @@
       <c r="JY13" s="0"/>
     </row>
     <row r="14" spans="1:285" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="87">
+      <c r="A14" s="93">
         <f>A12+1</f>
         <v>45603</v>
       </c>
@@ -3826,14 +3784,12 @@
         <v>3.5</v>
       </c>
       <c r="F14" s="8"/>
-      <c r="G14" s="11">
-        <v>3.5</v>
-      </c>
+      <c r="G14" s="11"/>
       <c r="H14" s="32"/>
       <c r="I14" s="26"/>
     </row>
     <row r="15" spans="1:285" s="1" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="87"/>
+      <c r="A15" s="93"/>
       <c r="B15" s="20" t="s">
         <v>3</v>
       </c>
@@ -3846,9 +3802,7 @@
         <v>7.5</v>
       </c>
       <c r="F15" s="16"/>
-      <c r="G15" s="13">
-        <v>7.5</v>
-      </c>
+      <c r="G15" s="13"/>
       <c r="H15" s="32"/>
       <c r="I15" s="26"/>
       <c r="J15" s="0"/>
@@ -4129,7 +4083,7 @@
       <c r="JY15" s="0"/>
     </row>
     <row r="16" spans="1:285" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="87">
+      <c r="A16" s="93">
         <f>A14+1</f>
         <v>45604</v>
       </c>
@@ -4140,9 +4094,7 @@
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="D16" s="48">
-        <v>4.5</v>
-      </c>
+      <c r="D16" s="48"/>
       <c r="E16" s="11"/>
       <c r="F16" s="8">
         <v>4.5</v>
@@ -4152,7 +4104,7 @@
       <c r="I16" s="27"/>
     </row>
     <row r="17" spans="1:291" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="87"/>
+      <c r="A17" s="93"/>
       <c r="B17" s="20" t="s">
         <v>7</v>
       </c>
@@ -4160,21 +4112,17 @@
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="D17" s="47">
-        <v>10</v>
-      </c>
+      <c r="D17" s="47"/>
       <c r="E17" s="10">
         <v>10</v>
       </c>
-      <c r="F17" s="15">
-        <v>10</v>
-      </c>
+      <c r="F17" s="15"/>
       <c r="G17" s="15"/>
       <c r="H17" s="38"/>
       <c r="I17" s="28"/>
     </row>
     <row r="18" spans="1:291" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="92">
+      <c r="A18" s="96">
         <f>A16+1</f>
         <v>45605</v>
       </c>
@@ -4185,9 +4133,7 @@
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="D18" s="50">
-        <v>7</v>
-      </c>
+      <c r="D18" s="50"/>
       <c r="E18" s="9"/>
       <c r="F18" s="7">
         <v>7</v>
@@ -4197,7 +4143,7 @@
       <c r="I18" s="26"/>
     </row>
     <row r="19" spans="1:291" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="92"/>
+      <c r="A19" s="96"/>
       <c r="B19" s="21" t="s">
         <v>7</v>
       </c>
@@ -4205,9 +4151,7 @@
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="D19" s="52">
-        <v>10</v>
-      </c>
+      <c r="D19" s="52"/>
       <c r="E19" s="22"/>
       <c r="F19" s="23"/>
       <c r="G19" s="52">
@@ -4217,7 +4161,7 @@
       <c r="I19" s="26"/>
     </row>
     <row r="20" spans="1:291" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="92">
+      <c r="A20" s="96">
         <f>A18+1</f>
         <v>45606</v>
       </c>
@@ -4228,9 +4172,7 @@
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="D20" s="48">
-        <v>7</v>
-      </c>
+      <c r="D20" s="48"/>
       <c r="E20" s="11"/>
       <c r="F20" s="8"/>
       <c r="G20" s="48">
@@ -4240,7 +4182,7 @@
       <c r="I20" s="26"/>
     </row>
     <row r="21" spans="1:291" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="92"/>
+      <c r="A21" s="96"/>
       <c r="B21" s="20" t="s">
         <v>3</v>
       </c>
@@ -4248,12 +4190,8 @@
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="D21" s="12">
-        <v>7.5</v>
-      </c>
-      <c r="E21" s="12">
-        <v>7.5</v>
-      </c>
+      <c r="D21" s="12"/>
+      <c r="E21" s="12"/>
       <c r="F21" s="14"/>
       <c r="G21" s="12">
         <v>7.5</v>
@@ -4262,7 +4200,7 @@
       <c r="I21" s="26"/>
     </row>
     <row r="22" spans="1:291" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="87">
+      <c r="A22" s="93">
         <f>A20+1</f>
         <v>45607</v>
       </c>
@@ -4273,21 +4211,17 @@
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="D22" s="11">
-        <v>3.5</v>
-      </c>
+      <c r="D22" s="11"/>
       <c r="E22" s="11">
         <v>3.5</v>
       </c>
       <c r="F22" s="8"/>
-      <c r="G22" s="11">
-        <v>3.5</v>
-      </c>
+      <c r="G22" s="11"/>
       <c r="H22" s="32"/>
       <c r="I22" s="26"/>
     </row>
     <row r="23" spans="1:291" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="87"/>
+      <c r="A23" s="93"/>
       <c r="B23" s="20" t="s">
         <v>3</v>
       </c>
@@ -4295,12 +4229,8 @@
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="D23" s="12">
-        <v>7.5</v>
-      </c>
-      <c r="E23" s="12">
-        <v>7.5</v>
-      </c>
+      <c r="D23" s="12"/>
+      <c r="E23" s="12"/>
       <c r="F23" s="14"/>
       <c r="G23" s="12">
         <v>7.5</v>
@@ -4309,7 +4239,7 @@
       <c r="I23" s="26"/>
     </row>
     <row r="24" spans="1:291" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="87">
+      <c r="A24" s="93">
         <f>A22+1</f>
         <v>45608</v>
       </c>
@@ -4323,18 +4253,14 @@
       <c r="D24" s="9">
         <v>3.5</v>
       </c>
-      <c r="E24" s="9">
-        <v>3.5</v>
-      </c>
-      <c r="F24" s="7">
-        <v>3.5</v>
-      </c>
+      <c r="E24" s="9"/>
+      <c r="F24" s="7"/>
       <c r="G24" s="7"/>
       <c r="H24" s="32"/>
       <c r="I24" s="26"/>
     </row>
     <row r="25" spans="1:291" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="87"/>
+      <c r="A25" s="93"/>
       <c r="B25" s="25" t="s">
         <v>3</v>
       </c>
@@ -4342,12 +4268,8 @@
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="D25" s="10">
-        <v>7.5</v>
-      </c>
-      <c r="E25" s="10">
-        <v>7.5</v>
-      </c>
+      <c r="D25" s="10"/>
+      <c r="E25" s="10"/>
       <c r="F25" s="15">
         <v>7.5</v>
       </c>
@@ -4356,7 +4278,7 @@
       <c r="I25" s="26"/>
     </row>
     <row r="26" spans="1:291" s="4" customFormat="1" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A26" s="87">
+      <c r="A26" s="93">
         <f>A24+1</f>
         <v>45609</v>
       </c>
@@ -4367,12 +4289,8 @@
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="D26" s="11">
-        <v>3.5</v>
-      </c>
-      <c r="E26" s="11">
-        <v>3.5</v>
-      </c>
+      <c r="D26" s="11"/>
+      <c r="E26" s="11"/>
       <c r="F26" s="8"/>
       <c r="G26" s="11">
         <v>3.5</v>
@@ -4663,7 +4581,7 @@
       <c r="KE26" s="29"/>
     </row>
     <row r="27" spans="1:291" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="87"/>
+      <c r="A27" s="93"/>
       <c r="B27" s="17" t="s">
         <v>3</v>
       </c>
@@ -4674,17 +4592,13 @@
       <c r="D27" s="13">
         <v>7.5</v>
       </c>
-      <c r="E27" s="13">
-        <v>7.5</v>
-      </c>
+      <c r="E27" s="13"/>
       <c r="F27" s="16"/>
-      <c r="G27" s="13">
-        <v>7.5</v>
-      </c>
+      <c r="G27" s="13"/>
       <c r="H27" s="40"/>
     </row>
     <row r="28" spans="1:291" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="88">
+      <c r="A28" s="98">
         <f>A26+1</f>
         <v>45610</v>
       </c>
@@ -4695,20 +4609,16 @@
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="D28" s="11">
-        <v>3.5</v>
-      </c>
+      <c r="D28" s="11"/>
       <c r="E28" s="11">
         <v>3.5</v>
       </c>
       <c r="F28" s="8"/>
-      <c r="G28" s="11">
-        <v>3.5</v>
-      </c>
+      <c r="G28" s="11"/>
       <c r="H28" s="33"/>
     </row>
     <row r="29" spans="1:291" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="89"/>
+      <c r="A29" s="99"/>
       <c r="B29" s="20" t="s">
         <v>3</v>
       </c>
@@ -4716,12 +4626,8 @@
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="D29" s="13">
-        <v>7.5</v>
-      </c>
-      <c r="E29" s="13">
-        <v>7.5</v>
-      </c>
+      <c r="D29" s="13"/>
+      <c r="E29" s="13"/>
       <c r="F29" s="16"/>
       <c r="G29" s="13">
         <v>7.5</v>
@@ -4729,7 +4635,7 @@
       <c r="H29" s="33"/>
     </row>
     <row r="30" spans="1:291" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="93">
+      <c r="A30" s="100">
         <f>A28+1</f>
         <v>45611</v>
       </c>
@@ -4740,20 +4646,16 @@
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="D30" s="47">
-        <v>10</v>
-      </c>
+      <c r="D30" s="47"/>
       <c r="E30" s="48">
         <v>4.5</v>
       </c>
       <c r="F30" s="8"/>
-      <c r="G30" s="48">
-        <v>4.5</v>
-      </c>
+      <c r="G30" s="48"/>
       <c r="H30" s="33"/>
     </row>
     <row r="31" spans="1:291" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="94"/>
+      <c r="A31" s="101"/>
       <c r="B31" s="20" t="s">
         <v>7</v>
       </c>
@@ -4761,12 +4663,8 @@
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="D31" s="50">
-        <v>7</v>
-      </c>
-      <c r="E31" s="47">
-        <v>10</v>
-      </c>
+      <c r="D31" s="50"/>
+      <c r="E31" s="47"/>
       <c r="F31" s="15"/>
       <c r="G31" s="47">
         <v>10</v>
@@ -4774,7 +4672,7 @@
       <c r="H31" s="33"/>
     </row>
     <row r="32" spans="1:291" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="92">
+      <c r="A32" s="96">
         <f>A30+1</f>
         <v>45612</v>
       </c>
@@ -4788,17 +4686,13 @@
       <c r="D32" s="52">
         <v>10</v>
       </c>
-      <c r="E32" s="50">
-        <v>7</v>
-      </c>
+      <c r="E32" s="50"/>
       <c r="F32" s="7"/>
-      <c r="G32" s="50">
-        <v>7</v>
-      </c>
+      <c r="G32" s="50"/>
       <c r="H32" s="33"/>
     </row>
     <row r="33" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="92"/>
+      <c r="A33" s="96"/>
       <c r="B33" s="17" t="s">
         <v>7</v>
       </c>
@@ -4807,19 +4701,15 @@
         <v>3</v>
       </c>
       <c r="D33" s="53"/>
-      <c r="E33" s="52">
-        <v>10</v>
-      </c>
+      <c r="E33" s="52"/>
       <c r="F33" s="6">
         <v>10</v>
       </c>
-      <c r="G33" s="52">
-        <v>10</v>
-      </c>
+      <c r="G33" s="52"/>
       <c r="H33" s="33"/>
     </row>
     <row r="34" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="92">
+      <c r="A34" s="96">
         <f>A32+1</f>
         <v>45613</v>
       </c>
@@ -4831,19 +4721,15 @@
         <v>3</v>
       </c>
       <c r="D34" s="50"/>
-      <c r="E34" s="48">
-        <v>7</v>
-      </c>
+      <c r="E34" s="48"/>
       <c r="F34" s="7">
         <v>7</v>
       </c>
-      <c r="G34" s="48">
-        <v>7</v>
-      </c>
+      <c r="G34" s="48"/>
       <c r="H34" s="33"/>
     </row>
     <row r="35" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="85"/>
+      <c r="A35" s="97"/>
       <c r="B35" s="79" t="s">
         <v>3</v>
       </c>
@@ -4856,9 +4742,7 @@
         <v>7.5</v>
       </c>
       <c r="F35" s="16"/>
-      <c r="G35" s="12">
-        <v>7.5</v>
-      </c>
+      <c r="G35" s="12"/>
       <c r="H35" s="33"/>
     </row>
     <row r="36" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -4872,10 +4756,10 @@
       <c r="H36" s="33"/>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A37" s="97" t="s">
+      <c r="A37" s="94" t="s">
         <v>27</v>
       </c>
-      <c r="B37" s="98"/>
+      <c r="B37" s="95"/>
       <c r="C37" s="64" t="s">
         <v>11</v>
       </c>
@@ -4894,8 +4778,8 @@
       <c r="H37" s="32"/>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A38" s="97"/>
-      <c r="B38" s="98"/>
+      <c r="A38" s="94"/>
+      <c r="B38" s="95"/>
       <c r="C38" s="65" t="s">
         <v>12</v>
       </c>
@@ -4914,26 +4798,26 @@
       <c r="H38" s="32"/>
     </row>
     <row r="39" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A39" s="97"/>
-      <c r="B39" s="98"/>
+      <c r="A39" s="94"/>
+      <c r="B39" s="95"/>
       <c r="C39" s="62" t="s">
         <v>13</v>
       </c>
       <c r="D39" s="76">
         <f>SUM(D2:D35)</f>
-        <v>155.5</v>
+        <v>165.5</v>
       </c>
       <c r="E39" s="77">
         <f>SUM(E2:E35)</f>
-        <v>158</v>
+        <v>144</v>
       </c>
       <c r="F39" s="77">
         <f>SUM(F2:F35)</f>
-        <v>120</v>
+        <v>82</v>
       </c>
       <c r="G39" s="78">
         <f>SUM(G2:G35)</f>
-        <v>153.5</v>
+        <v>129</v>
       </c>
       <c r="H39" s="32"/>
     </row>
@@ -4969,6 +4853,13 @@
     </row>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="A2:A3"/>
+    <mergeCell ref="A14:A15"/>
+    <mergeCell ref="A8:A9"/>
+    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="A6:A7"/>
+    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A12:A13"/>
     <mergeCell ref="A16:A17"/>
     <mergeCell ref="A37:B39"/>
     <mergeCell ref="A34:A35"/>
@@ -4980,13 +4871,6 @@
     <mergeCell ref="A24:A25"/>
     <mergeCell ref="A30:A31"/>
     <mergeCell ref="A32:A33"/>
-    <mergeCell ref="A2:A3"/>
-    <mergeCell ref="A14:A15"/>
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
-    <mergeCell ref="A12:A13"/>
   </mergeCells>
   <conditionalFormatting sqref="C2:C35">
     <cfRule type="colorScale" priority="2">
